--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_58_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_58_IN_Piura.xlsx
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>2.55</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="C12" s="30">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>80.92</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>16.53</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1918,11 +1918,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>11.4748</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1943,11 +1943,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>0.2924</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>2.55</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1968,11 +1968,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>11.1824</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>97.45</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>11.48</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2270,6 +2270,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2418,6 +2419,7 @@
       <c r="F13" s="17" t="inlineStr"/>
       <c r="G13" s="17" t="inlineStr"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -2462,6 +2464,7 @@
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="120" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
@@ -2681,11 +2684,11 @@
       </c>
       <c r="B12" s="32">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>62.44</v>
       </c>
       <c r="C12" s="23">
         <f>SUM(C10:C11)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -2695,19 +2698,19 @@
       <c r="E12" s="17" t="inlineStr"/>
       <c r="F12" s="17">
         <f>ROUND(AVERAGE(F10:F11),2)</f>
-        <v/>
+        <v>17.44</v>
       </c>
       <c r="G12" s="22">
         <f>ROUND(AVERAGE(G10:G11),4)</f>
-        <v/>
+        <v>0.4027</v>
       </c>
       <c r="H12" s="23">
         <f>ROUND(AVERAGE(H10:H11),2)</f>
-        <v/>
+        <v>0.29</v>
       </c>
       <c r="I12" s="23">
         <f>ROUND(AVERAGE(I10:I11),2)</f>
-        <v/>
+        <v>95.66</v>
       </c>
     </row>
     <row r="13"/>
